--- a/IF +IFS +AND +OR.xlsx
+++ b/IF +IFS +AND +OR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prabh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a069205656c65a3/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C99D5FF-05FF-4DD2-9178-2F641FD3280E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62BEDB8B-4B1E-47F8-904D-F66F1C0C5B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6371BE39-685B-42FE-B5CC-9CD800A052B1}"/>
   </bookViews>
@@ -31,15 +31,49 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="170">
   <si>
     <t>Emp ID</t>
   </si>
@@ -1695,6 +1729,90 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>Salary Status</t>
+  </si>
+  <si>
+    <t>Coffee Status</t>
+  </si>
+  <si>
+    <t>Attendance status</t>
+  </si>
+  <si>
+    <t>Search Actvty</t>
+  </si>
+  <si>
+    <t>Mood check</t>
+  </si>
+  <si>
+    <t>Food check</t>
+  </si>
+  <si>
+    <t>Department Check</t>
+  </si>
+  <si>
+    <t>Salary Category</t>
+  </si>
+  <si>
+    <t>Coffee Category</t>
+  </si>
+  <si>
+    <t>Bun Category</t>
+  </si>
+  <si>
+    <t>Google Search Category</t>
+  </si>
+  <si>
+    <t>Employee Grade</t>
+  </si>
+  <si>
+    <t>Employee Activity</t>
+  </si>
+  <si>
+    <t>Coffee Rating</t>
+  </si>
+  <si>
+    <t>Employee Eligibility</t>
+  </si>
+  <si>
+    <t>Employee Attention</t>
+  </si>
+  <si>
+    <t>Active Employee</t>
+  </si>
+  <si>
+    <t>Happy Employee</t>
+  </si>
+  <si>
+    <t>Technical Employee</t>
+  </si>
+  <si>
+    <t>Pizza Fan</t>
+  </si>
+  <si>
+    <t>Responsible Employee</t>
+  </si>
+  <si>
+    <t>Special Employee</t>
+  </si>
+  <si>
+    <t>Coffee/Food Lover</t>
+  </si>
+  <si>
+    <t>Very Active Employee</t>
+  </si>
+  <si>
+    <t>Good Mood</t>
+  </si>
+  <si>
+    <t>Technical Department</t>
+  </si>
+  <si>
+    <t>High Performer</t>
+  </si>
+  <si>
+    <t>Reward Eligibility</t>
   </si>
 </sst>
 </file>
@@ -1723,12 +1841,18 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1743,15 +1867,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1761,8 +1882,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1779,6 +1910,68 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>8</v>
+    <v>0</v>
+    <v>3</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2098,7 +2291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B419E4B-5A9B-49BA-AEBB-2E825F019CE2}">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:AU129"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2109,541 +2302,2344 @@
     <col min="6" max="6" width="20.33203125" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
     <col min="8" max="8" width="31.44140625" customWidth="1"/>
-    <col min="13" max="13" width="79.5546875" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" customWidth="1"/>
+    <col min="12" max="16" width="16.88671875" customWidth="1"/>
+    <col min="17" max="17" width="20.6640625" customWidth="1"/>
+    <col min="18" max="45" width="16.88671875" customWidth="1"/>
+    <col min="47" max="47" width="79.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:47" ht="28.8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="J1" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG1" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH1" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI1" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK1" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
+      <c r="AP1" s="6"/>
+      <c r="AQ1" s="6"/>
+      <c r="AR1" s="6"/>
+      <c r="AS1" s="6"/>
+      <c r="AU1" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:47">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="1">
         <v>30000</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="1">
         <v>3</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="1">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="1">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M2" t="s">
+      <c r="J2" s="7" t="str" cm="1">
+        <f t="array" ref="J2:J16">IF(D2:D16&gt;=40000,"High Salary","Normal salary")</f>
+        <v>Normal salary</v>
+      </c>
+      <c r="K2" s="7" t="str" cm="1">
+        <f t="array" ref="K2:K16">IF(E2:E16&gt;=4,"Heavy Coffee Driner","Normal ")</f>
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L2" s="7" t="str" cm="1">
+        <f t="array" ref="L2:L16">IF(F2:F16&gt;=3,"Poor Attendance","Good Attendance")</f>
+        <v>Good Attendance</v>
+      </c>
+      <c r="M2" s="7" t="str" cm="1">
+        <f t="array" ref="M2:M16">IF(G2:G16&gt;=20,"High Search","Normal  search")</f>
+        <v>Normal  search</v>
+      </c>
+      <c r="N2" s="7" t="str" cm="1">
+        <f t="array" ref="N2:N16">IF(C2:C16="Python","Pyhton Employee","Other Department ")</f>
+        <v>Pyhton Employee</v>
+      </c>
+      <c r="O2" s="7" t="str" cm="1">
+        <f t="array" ref="O2:O16">IF(H2:H16&gt;="Pizza","Pizza lower","Other Food")</f>
+        <v>Pizza lower</v>
+      </c>
+      <c r="P2" s="7" t="str" cm="1">
+        <f t="array" ref="P2:P16">IF(I2:I16&gt;="Happy","Good Mood","Other Mood ")</f>
+        <v>Good Mood</v>
+      </c>
+      <c r="Q2" s="7" t="str" cm="1">
+        <f t="array" ref="Q2">_xlfn.IFS(D2&gt;=50000, "Excellent", D2&gt;=40000, "Very Good", D2&gt;=30000, "Good", D2&lt;30000, "Low")</f>
+        <v>Good</v>
+      </c>
+      <c r="R2" s="7" t="str" cm="1">
+        <f t="array" ref="R2">_xlfn.IFS(E2&gt;=5, "Heavy", E2&gt;=3, "Moderate", E2&gt;=1, "Normal", E2=0, "No Coffee")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="S2" s="7" t="str" cm="1">
+        <f t="array" ref="S2">_xlfn.IFS(F3&gt;=5, "Very High", F3&gt;=3, "high", F3&gt;=1, "Moderate", F3=0, "No Bunk")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="T2" s="7" t="str" cm="1">
+        <f t="array" ref="T2">_xlfn.IFS(G2&gt;=30, "Very Hgh", G2&gt;=20, "Hgh", G2&gt;=10, "Moderate", G2&lt;10, "Low")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="U2" s="7" t="str" cm="1">
+        <f t="array" ref="U2">_xlfn.IFS(D2&gt;=50000, "A", D2&gt;=40000, "B", D2&gt;=30000, "C", D2&lt;30000, "D")</f>
+        <v>C</v>
+      </c>
+      <c r="V2" s="7" t="str" cm="1">
+        <f t="array" ref="V2">_xlfn.IFS(G2&gt;=30, "Very Active", G2&gt;=20, "Active", G2&gt;=10, "Moderate", G2&lt;10, "Less Active")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="W2" s="7" t="str" cm="1">
+        <f t="array" ref="W2">_xlfn.IFS(E2&gt;=5, "Coffee Addict", E2&gt;=4, "Heavy Drinker", E2&gt;=2, "Regular Drinker", E2&lt;2, "light drinker")</f>
+        <v>Regular Drinker</v>
+      </c>
+      <c r="X2" s="7" t="str">
+        <f>IF(AND(D2&gt;=35000, C2="Python"),"Elgble","Not Elgble")</f>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y2" s="7" t="str">
+        <f>IF(AND(E2&gt;=4, F2&gt;=3),"Needs Attenton","Normal")</f>
+        <v>Normal</v>
+      </c>
+      <c r="Z2" s="7" t="str">
+        <f>IF(AND(G2&gt;=20, F2&lt;=2),"Active Employee","inactive")</f>
+        <v>inactive</v>
+      </c>
+      <c r="AA2" s="7" t="str">
+        <f>IF(AND(I2="Happy", D2&lt;=35000),"Happy High Earner","Normal Employee")</f>
+        <v>Happy High Earner</v>
+      </c>
+      <c r="AB2" s="7" t="str">
+        <f>IF(AND(C2="Python", D2&gt;=30000), "Python Performer", "Other")</f>
+        <v>Python Performer</v>
+      </c>
+      <c r="AC2" s="7" t="str">
+        <f>IF(AND(H2="Pizza", I2="Happy"), "Pizza Fan", "Not Pizza Fan")</f>
+        <v>Pizza Fan</v>
+      </c>
+      <c r="AD2" s="7" t="str">
+        <f>IF(AND(E2&lt;=2, D2&gt;=35000), "Responsible", "Needs Improvement")</f>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE2" s="7" t="str">
+        <f>IF(OR(D2&gt;=50000, C2="Python"), "Special Employee", "Regular Employee")</f>
+        <v>Special Employee</v>
+      </c>
+      <c r="AF2" s="7" t="str">
+        <f>IF(OR(F2&gt;=5, H2="Pizza"), "Food &amp; Coffee Lover", "Normal")</f>
+        <v>Food &amp; Coffee Lover</v>
+      </c>
+      <c r="AG2" s="7" t="str">
+        <f>IF(OR(G2&gt;=30, E2=0), "Very Active", "Normal")</f>
+        <v>Normal</v>
+      </c>
+      <c r="AH2" s="7" t="str">
+        <f>IF(OR(I2="Happy", I2="Excited"), "Good Mood", "Other Mood")</f>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI2" s="7" t="str">
+        <f>IF(OR(C2="Python", C2="SQL"), "Technical", "Other")</f>
+        <v>Technical</v>
+      </c>
+      <c r="AJ2" s="7" t="str">
+        <f>IF(OR(D2&gt;=50000, G2&gt;=30), "High Performer", "Regular Performer")</f>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK2" s="7" t="str">
+        <f>IF(OR(D2&gt;=40000, E2=0, I2="Happy"), "Reward", "No Reward")</f>
+        <v>Reward</v>
+      </c>
+      <c r="AL2" s="7"/>
+      <c r="AM2" s="7"/>
+      <c r="AN2" s="7"/>
+      <c r="AO2" s="7"/>
+      <c r="AP2" s="7"/>
+      <c r="AQ2" s="7"/>
+      <c r="AR2" s="7"/>
+      <c r="AS2" s="7"/>
+      <c r="AU2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:47">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="1">
         <v>40000</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>5</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3" t="s">
+      <c r="J3" s="7" t="str">
+        <v>High Salary</v>
+      </c>
+      <c r="K3" s="7" t="str">
+        <v>Heavy Coffee Driner</v>
+      </c>
+      <c r="L3" s="7" t="str">
+        <v>Good Attendance</v>
+      </c>
+      <c r="M3" s="7" t="str">
+        <v>Normal  search</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O3" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P3" s="7" t="str">
+        <v xml:space="preserve">Other Mood </v>
+      </c>
+      <c r="Q3" s="7" t="str" cm="1">
+        <f t="array" ref="Q3">_xlfn.IFS(D3&gt;=50000, "Excellent", D3&gt;=40000, "Very Good", D3&gt;=30000, "Good", D3&lt;30000, "Low")</f>
+        <v>Very Good</v>
+      </c>
+      <c r="R3" s="7" t="str" cm="1">
+        <f t="array" ref="R3">_xlfn.IFS(E3&gt;=5, "Heavy", E3&gt;=3, "Moderate", E3&gt;=1, "Normal", E3=0, "No Coffee")</f>
+        <v>Heavy</v>
+      </c>
+      <c r="S3" s="7" t="str" cm="1">
+        <f t="array" ref="S3">_xlfn.IFS(F4&gt;=5, "Very High", F4&gt;=3, "high", F4&gt;=1, "Moderate", F4=0, "No Bunk")</f>
+        <v>high</v>
+      </c>
+      <c r="T3" s="7" t="str" cm="1">
+        <f t="array" ref="T3">_xlfn.IFS(G3&gt;=30, "Very Hgh", G3&gt;=20, "Hgh", G3&gt;=10, "Moderate", G3&lt;10, "Low")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="U3" s="7" t="str" cm="1">
+        <f t="array" ref="U3">_xlfn.IFS(D3&gt;=50000, "A", D3&gt;=40000, "B", D3&gt;=30000, "C", D3&lt;30000, "D")</f>
+        <v>B</v>
+      </c>
+      <c r="V3" s="7" t="str" cm="1">
+        <f t="array" ref="V3">_xlfn.IFS(G3&gt;=30, "Very Active", G3&gt;=20, "Active", G3&gt;=10, "Moderate", G3&lt;10, "Less Active")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="W3" s="7" t="str" cm="1">
+        <f t="array" ref="W3">_xlfn.IFS(E3&gt;=5, "Coffee Addict", E3&gt;=4, "Heavy Drinker", E3&gt;=2, "Regular Drinker", E3&lt;2, "light drinker")</f>
+        <v>Coffee Addict</v>
+      </c>
+      <c r="X3" s="7" t="str">
+        <f t="shared" ref="X3:X16" si="0">IF(AND(D3&gt;=35000, C3="Python"),"Elgble","Not Elgble")</f>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y3" s="7" t="str">
+        <f t="shared" ref="Y3:Y16" si="1">IF(AND(E3&gt;=4, F3&gt;=3),"Needs Attenton","Normal")</f>
+        <v>Normal</v>
+      </c>
+      <c r="Z3" s="7" t="str">
+        <f t="shared" ref="Z3:Z16" si="2">IF(AND(G3&gt;=20, F3&lt;=2),"Active Employee","inactive")</f>
+        <v>inactive</v>
+      </c>
+      <c r="AA3" s="7" t="str">
+        <f t="shared" ref="AA3:AA16" si="3">IF(AND(I3="Happy", D3&lt;=35000),"Happy High Earner","Normal Employee")</f>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB3" s="7" t="str">
+        <f t="shared" ref="AB3:AB16" si="4">IF(AND(C3="Python", D3&gt;=30000), "Python Performer", "Other")</f>
+        <v>Other</v>
+      </c>
+      <c r="AC3" s="7" t="str">
+        <f t="shared" ref="AC3:AC16" si="5">IF(AND(H3="Pizza", I3="Happy"), "Pizza Fan", "Not Pizza Fan")</f>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD3" s="7" t="str">
+        <f t="shared" ref="AD3:AD16" si="6">IF(AND(E3&lt;=2, D3&gt;=35000), "Responsible", "Needs Improvement")</f>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE3" s="7" t="str">
+        <f t="shared" ref="AE3:AE16" si="7">IF(OR(D3&gt;=50000, C3="Python"), "Special Employee", "Regular Employee")</f>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF3" s="7" t="str">
+        <f t="shared" ref="AF3:AF16" si="8">IF(OR(F3&gt;=5, H3="Pizza"), "Food &amp; Coffee Lover", "Normal")</f>
+        <v>Normal</v>
+      </c>
+      <c r="AG3" s="7" t="str">
+        <f t="shared" ref="AG3:AG16" si="9">IF(OR(G3&gt;=30, E3=0), "Very Active", "Normal")</f>
+        <v>Normal</v>
+      </c>
+      <c r="AH3" s="7" t="str">
+        <f t="shared" ref="AH3:AH16" si="10">IF(OR(I3="Happy", I3="Excited"), "Good Mood", "Other Mood")</f>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI3" s="7" t="str">
+        <f t="shared" ref="AI3:AI16" si="11">IF(OR(C3="Python", C3="SQL"), "Technical", "Other")</f>
+        <v>Other</v>
+      </c>
+      <c r="AJ3" s="7" t="str">
+        <f t="shared" ref="AJ3:AJ16" si="12">IF(OR(D3&gt;=50000, G3&gt;=30), "High Performer", "Regular Performer")</f>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK3" s="7" t="str">
+        <f t="shared" ref="AK3:AK16" si="13">IF(OR(D3&gt;=40000, E3=0, I3="Happy"), "Reward", "No Reward")</f>
+        <v>Reward</v>
+      </c>
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="7"/>
+      <c r="AN3" s="7"/>
+      <c r="AO3" s="7"/>
+      <c r="AP3" s="7"/>
+      <c r="AQ3" s="7"/>
+      <c r="AR3" s="7"/>
+      <c r="AS3" s="7"/>
+      <c r="AU3" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="AU3" ca="1">IF(D:D&gt;=40000,"High Salary","Normal salary")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <v>35000</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <v>4</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="1">
         <v>25</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="J4" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K4" s="7" t="str">
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L4" s="7" t="str">
+        <v>Poor Attendance</v>
+      </c>
+      <c r="M4" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N4" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O4" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P4" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q4" s="7" t="str" cm="1">
+        <f t="array" ref="Q4">_xlfn.IFS(D4&gt;=50000, "Excellent", D4&gt;=40000, "Very Good", D4&gt;=30000, "Good", D4&lt;30000, "Low")</f>
+        <v>Good</v>
+      </c>
+      <c r="R4" s="7" t="str" cm="1">
+        <f t="array" ref="R4">_xlfn.IFS(E4&gt;=5, "Heavy", E4&gt;=3, "Moderate", E4&gt;=1, "Normal", E4=0, "No Coffee")</f>
+        <v>Normal</v>
+      </c>
+      <c r="S4" s="7" t="str" cm="1">
+        <f t="array" ref="S4">_xlfn.IFS(F5&gt;=5, "Very High", F5&gt;=3, "high", F5&gt;=1, "Moderate", F5=0, "No Bunk")</f>
+        <v>high</v>
+      </c>
+      <c r="T4" s="7" t="str" cm="1">
+        <f t="array" ref="T4">_xlfn.IFS(G4&gt;=30, "Very Hgh", G4&gt;=20, "Hgh", G4&gt;=10, "Moderate", G4&lt;10, "Low")</f>
+        <v>Hgh</v>
+      </c>
+      <c r="U4" s="7" t="str" cm="1">
+        <f t="array" ref="U4">_xlfn.IFS(D4&gt;=50000, "A", D4&gt;=40000, "B", D4&gt;=30000, "C", D4&lt;30000, "D")</f>
+        <v>C</v>
+      </c>
+      <c r="V4" s="7" t="str" cm="1">
+        <f t="array" ref="V4">_xlfn.IFS(G4&gt;=30, "Very Active", G4&gt;=20, "Active", G4&gt;=10, "Moderate", G4&lt;10, "Less Active")</f>
+        <v>Active</v>
+      </c>
+      <c r="W4" s="7" t="str" cm="1">
+        <f t="array" ref="W4">_xlfn.IFS(E4&gt;=5, "Coffee Addict", E4&gt;=4, "Heavy Drinker", E4&gt;=2, "Regular Drinker", E4&lt;2, "light drinker")</f>
+        <v>Regular Drinker</v>
+      </c>
+      <c r="X4" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y4" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z4" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA4" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB4" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC4" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD4" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Responsible</v>
+      </c>
+      <c r="AE4" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF4" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Normal</v>
+      </c>
+      <c r="AG4" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH4" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Other Mood</v>
+      </c>
+      <c r="AI4" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Technical</v>
+      </c>
+      <c r="AJ4" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK4" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>No Reward</v>
+      </c>
+      <c r="AL4" s="7"/>
+      <c r="AM4" s="7"/>
+      <c r="AN4" s="7"/>
+      <c r="AO4" s="7"/>
+      <c r="AP4" s="7"/>
+      <c r="AQ4" s="7"/>
+      <c r="AR4" s="7"/>
+      <c r="AS4" s="7"/>
+      <c r="AU4" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:47">
+      <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>28000</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="1">
         <v>8</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M5" t="s">
+      <c r="J5" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K5" s="7" t="str">
+        <v>Heavy Coffee Driner</v>
+      </c>
+      <c r="L5" s="7" t="str">
+        <v>Poor Attendance</v>
+      </c>
+      <c r="M5" s="7" t="str">
+        <v>Normal  search</v>
+      </c>
+      <c r="N5" s="7" t="str">
+        <v>Pyhton Employee</v>
+      </c>
+      <c r="O5" s="7" t="str">
+        <v>Pizza lower</v>
+      </c>
+      <c r="P5" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q5" s="7" t="str" cm="1">
+        <f t="array" ref="Q5">_xlfn.IFS(D5&gt;=50000, "Excellent", D5&gt;=40000, "Very Good", D5&gt;=30000, "Good", D5&lt;30000, "Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="R5" s="7" t="str" cm="1">
+        <f t="array" ref="R5">_xlfn.IFS(E5&gt;=5, "Heavy", E5&gt;=3, "Moderate", E5&gt;=1, "Normal", E5=0, "No Coffee")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="S5" s="7" t="str" cm="1">
+        <f t="array" ref="S5">_xlfn.IFS(F6&gt;=5, "Very High", F6&gt;=3, "high", F6&gt;=1, "Moderate", F6=0, "No Bunk")</f>
+        <v>No Bunk</v>
+      </c>
+      <c r="T5" s="7" t="str" cm="1">
+        <f t="array" ref="T5">_xlfn.IFS(G5&gt;=30, "Very Hgh", G5&gt;=20, "Hgh", G5&gt;=10, "Moderate", G5&lt;10, "Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="U5" s="7" t="str" cm="1">
+        <f t="array" ref="U5">_xlfn.IFS(D5&gt;=50000, "A", D5&gt;=40000, "B", D5&gt;=30000, "C", D5&lt;30000, "D")</f>
+        <v>D</v>
+      </c>
+      <c r="V5" s="7" t="str" cm="1">
+        <f t="array" ref="V5">_xlfn.IFS(G5&gt;=30, "Very Active", G5&gt;=20, "Active", G5&gt;=10, "Moderate", G5&lt;10, "Less Active")</f>
+        <v>Less Active</v>
+      </c>
+      <c r="W5" s="7" t="str" cm="1">
+        <f t="array" ref="W5">_xlfn.IFS(E5&gt;=5, "Coffee Addict", E5&gt;=4, "Heavy Drinker", E5&gt;=2, "Regular Drinker", E5&lt;2, "light drinker")</f>
+        <v>Heavy Drinker</v>
+      </c>
+      <c r="X5" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y5" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Attenton</v>
+      </c>
+      <c r="Z5" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA5" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Happy High Earner</v>
+      </c>
+      <c r="AB5" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC5" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Pizza Fan</v>
+      </c>
+      <c r="AD5" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE5" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Special Employee</v>
+      </c>
+      <c r="AF5" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Food &amp; Coffee Lover</v>
+      </c>
+      <c r="AG5" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH5" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI5" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Technical</v>
+      </c>
+      <c r="AJ5" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK5" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL5" s="7"/>
+      <c r="AM5" s="7"/>
+      <c r="AN5" s="7"/>
+      <c r="AO5" s="7"/>
+      <c r="AP5" s="7"/>
+      <c r="AQ5" s="7"/>
+      <c r="AR5" s="7"/>
+      <c r="AS5" s="7"/>
+      <c r="AU5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:47">
+      <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>45000</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="1">
         <v>30</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3" t="s">
+      <c r="J6" s="7" t="str">
+        <v>High Salary</v>
+      </c>
+      <c r="K6" s="7" t="str">
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L6" s="7" t="str">
+        <v>Good Attendance</v>
+      </c>
+      <c r="M6" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N6" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O6" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P6" s="7" t="str">
+        <v xml:space="preserve">Other Mood </v>
+      </c>
+      <c r="Q6" s="7" t="str" cm="1">
+        <f t="array" ref="Q6">_xlfn.IFS(D6&gt;=50000, "Excellent", D6&gt;=40000, "Very Good", D6&gt;=30000, "Good", D6&lt;30000, "Low")</f>
+        <v>Very Good</v>
+      </c>
+      <c r="R6" s="7" t="str" cm="1">
+        <f t="array" ref="R6">_xlfn.IFS(E6&gt;=5, "Heavy", E6&gt;=3, "Moderate", E6&gt;=1, "Normal", E6=0, "No Coffee")</f>
+        <v>Normal</v>
+      </c>
+      <c r="S6" s="7" t="str" cm="1">
+        <f t="array" ref="S6">_xlfn.IFS(F7&gt;=5, "Very High", F7&gt;=3, "high", F7&gt;=1, "Moderate", F7=0, "No Bunk")</f>
+        <v>Very High</v>
+      </c>
+      <c r="T6" s="7" t="str" cm="1">
+        <f t="array" ref="T6">_xlfn.IFS(G6&gt;=30, "Very Hgh", G6&gt;=20, "Hgh", G6&gt;=10, "Moderate", G6&lt;10, "Low")</f>
+        <v>Very Hgh</v>
+      </c>
+      <c r="U6" s="7" t="str" cm="1">
+        <f t="array" ref="U6">_xlfn.IFS(D6&gt;=50000, "A", D6&gt;=40000, "B", D6&gt;=30000, "C", D6&lt;30000, "D")</f>
+        <v>B</v>
+      </c>
+      <c r="V6" s="7" t="str" cm="1">
+        <f t="array" ref="V6">_xlfn.IFS(G6&gt;=30, "Very Active", G6&gt;=20, "Active", G6&gt;=10, "Moderate", G6&lt;10, "Less Active")</f>
+        <v>Very Active</v>
+      </c>
+      <c r="W6" s="7" t="str" cm="1">
+        <f t="array" ref="W6">_xlfn.IFS(E6&gt;=5, "Coffee Addict", E6&gt;=4, "Heavy Drinker", E6&gt;=2, "Regular Drinker", E6&lt;2, "light drinker")</f>
+        <v>light drinker</v>
+      </c>
+      <c r="X6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y6" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z6" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Active Employee</v>
+      </c>
+      <c r="AA6" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB6" s="7" t="str">
+        <f>IF(AND(C6="Python", D6&gt;=30000), "Python Performer", "Other")</f>
+        <v>Other</v>
+      </c>
+      <c r="AC6" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD6" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Responsible</v>
+      </c>
+      <c r="AE6" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF6" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Normal</v>
+      </c>
+      <c r="AG6" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Very Active</v>
+      </c>
+      <c r="AH6" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI6" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Other</v>
+      </c>
+      <c r="AJ6" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>High Performer</v>
+      </c>
+      <c r="AK6" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL6" s="7"/>
+      <c r="AM6" s="7"/>
+      <c r="AN6" s="7"/>
+      <c r="AO6" s="7"/>
+      <c r="AP6" s="7"/>
+      <c r="AQ6" s="7"/>
+      <c r="AR6" s="7"/>
+      <c r="AS6" s="7"/>
+    </row>
+    <row r="7" spans="1:47">
+      <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>32000</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>3</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="1">
         <v>12</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="J7" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K7" s="7" t="str">
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L7" s="7" t="str">
+        <v>Poor Attendance</v>
+      </c>
+      <c r="M7" s="7" t="str">
+        <v>Normal  search</v>
+      </c>
+      <c r="N7" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O7" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P7" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q7" s="7" t="str" cm="1">
+        <f t="array" ref="Q7">_xlfn.IFS(D7&gt;=50000, "Excellent", D7&gt;=40000, "Very Good", D7&gt;=30000, "Good", D7&lt;30000, "Low")</f>
+        <v>Good</v>
+      </c>
+      <c r="R7" s="7" t="str" cm="1">
+        <f t="array" ref="R7">_xlfn.IFS(E7&gt;=5, "Heavy", E7&gt;=3, "Moderate", E7&gt;=1, "Normal", E7=0, "No Coffee")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="S7" s="7" t="str" cm="1">
+        <f t="array" ref="S7">_xlfn.IFS(F8&gt;=5, "Very High", F8&gt;=3, "high", F8&gt;=1, "Moderate", F8=0, "No Bunk")</f>
+        <v>Very High</v>
+      </c>
+      <c r="T7" s="7" t="str" cm="1">
+        <f t="array" ref="T7">_xlfn.IFS(G7&gt;=30, "Very Hgh", G7&gt;=20, "Hgh", G7&gt;=10, "Moderate", G7&lt;10, "Low")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="U7" s="7" t="str" cm="1">
+        <f t="array" ref="U7">_xlfn.IFS(D7&gt;=50000, "A", D7&gt;=40000, "B", D7&gt;=30000, "C", D7&lt;30000, "D")</f>
+        <v>C</v>
+      </c>
+      <c r="V7" s="7" t="str" cm="1">
+        <f t="array" ref="V7">_xlfn.IFS(G7&gt;=30, "Very Active", G7&gt;=20, "Active", G7&gt;=10, "Moderate", G7&lt;10, "Less Active")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="W7" s="7" t="str" cm="1">
+        <f t="array" ref="W7">_xlfn.IFS(E7&gt;=5, "Coffee Addict", E7&gt;=4, "Heavy Drinker", E7&gt;=2, "Regular Drinker", E7&lt;2, "light drinker")</f>
+        <v>Regular Drinker</v>
+      </c>
+      <c r="X7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y7" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z7" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA7" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Happy High Earner</v>
+      </c>
+      <c r="AB7" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC7" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD7" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE7" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF7" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Food &amp; Coffee Lover</v>
+      </c>
+      <c r="AG7" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH7" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI7" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Other</v>
+      </c>
+      <c r="AJ7" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK7" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="7"/>
+      <c r="AO7" s="7"/>
+      <c r="AP7" s="7"/>
+      <c r="AQ7" s="7"/>
+      <c r="AR7" s="7"/>
+      <c r="AS7" s="7"/>
+      <c r="AU7" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:47">
+      <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>25000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="1">
         <v>35</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M8" t="s">
+      <c r="J8" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K8" s="7" t="str">
+        <v>Heavy Coffee Driner</v>
+      </c>
+      <c r="L8" s="7" t="str">
+        <v>Poor Attendance</v>
+      </c>
+      <c r="M8" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N8" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O8" s="7" t="str">
+        <v>Pizza lower</v>
+      </c>
+      <c r="P8" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q8" s="7" t="str" cm="1">
+        <f t="array" ref="Q8">_xlfn.IFS(D8&gt;=50000, "Excellent", D8&gt;=40000, "Very Good", D8&gt;=30000, "Good", D8&lt;30000, "Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="R8" s="7" t="str" cm="1">
+        <f t="array" ref="R8">_xlfn.IFS(E8&gt;=5, "Heavy", E8&gt;=3, "Moderate", E8&gt;=1, "Normal", E8=0, "No Coffee")</f>
+        <v>Heavy</v>
+      </c>
+      <c r="S8" s="7" t="str" cm="1">
+        <f t="array" ref="S8">_xlfn.IFS(F9&gt;=5, "Very High", F9&gt;=3, "high", F9&gt;=1, "Moderate", F9=0, "No Bunk")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="T8" s="7" t="str" cm="1">
+        <f t="array" ref="T8">_xlfn.IFS(G8&gt;=30, "Very Hgh", G8&gt;=20, "Hgh", G8&gt;=10, "Moderate", G8&lt;10, "Low")</f>
+        <v>Very Hgh</v>
+      </c>
+      <c r="U8" s="7" t="str" cm="1">
+        <f t="array" ref="U8">_xlfn.IFS(D8&gt;=50000, "A", D8&gt;=40000, "B", D8&gt;=30000, "C", D8&lt;30000, "D")</f>
+        <v>D</v>
+      </c>
+      <c r="V8" s="7" t="str" cm="1">
+        <f t="array" ref="V8">_xlfn.IFS(G8&gt;=30, "Very Active", G8&gt;=20, "Active", G8&gt;=10, "Moderate", G8&lt;10, "Less Active")</f>
+        <v>Very Active</v>
+      </c>
+      <c r="W8" s="7" t="str" cm="1">
+        <f t="array" ref="W8">_xlfn.IFS(E8&gt;=5, "Coffee Addict", E8&gt;=4, "Heavy Drinker", E8&gt;=2, "Regular Drinker", E8&lt;2, "light drinker")</f>
+        <v>Coffee Addict</v>
+      </c>
+      <c r="X8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y8" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Attenton</v>
+      </c>
+      <c r="Z8" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA8" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB8" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC8" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD8" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE8" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF8" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Food &amp; Coffee Lover</v>
+      </c>
+      <c r="AG8" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Very Active</v>
+      </c>
+      <c r="AH8" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Other Mood</v>
+      </c>
+      <c r="AI8" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Technical</v>
+      </c>
+      <c r="AJ8" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>High Performer</v>
+      </c>
+      <c r="AK8" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>No Reward</v>
+      </c>
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="7"/>
+      <c r="AN8" s="7"/>
+      <c r="AO8" s="7"/>
+      <c r="AP8" s="7"/>
+      <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
+      <c r="AS8" s="7"/>
+      <c r="AU8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:47">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="1">
         <v>50000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="1">
         <v>20</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3" t="s">
+      <c r="J9" s="7" t="str">
+        <v>High Salary</v>
+      </c>
+      <c r="K9" s="7" t="str">
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L9" s="7" t="str">
+        <v>Good Attendance</v>
+      </c>
+      <c r="M9" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N9" s="7" t="str">
+        <v>Pyhton Employee</v>
+      </c>
+      <c r="O9" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P9" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q9" s="7" t="str" cm="1">
+        <f t="array" ref="Q9">_xlfn.IFS(D9&gt;=50000, "Excellent", D9&gt;=40000, "Very Good", D9&gt;=30000, "Good", D9&lt;30000, "Low")</f>
+        <v>Excellent</v>
+      </c>
+      <c r="R9" s="7" t="str" cm="1">
+        <f t="array" ref="R9">_xlfn.IFS(E9&gt;=5, "Heavy", E9&gt;=3, "Moderate", E9&gt;=1, "Normal", E9=0, "No Coffee")</f>
+        <v>Normal</v>
+      </c>
+      <c r="S9" s="7" t="str" cm="1">
+        <f t="array" ref="S9">_xlfn.IFS(F10&gt;=5, "Very High", F10&gt;=3, "high", F10&gt;=1, "Moderate", F10=0, "No Bunk")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="T9" s="7" t="str" cm="1">
+        <f t="array" ref="T9">_xlfn.IFS(G9&gt;=30, "Very Hgh", G9&gt;=20, "Hgh", G9&gt;=10, "Moderate", G9&lt;10, "Low")</f>
+        <v>Hgh</v>
+      </c>
+      <c r="U9" s="7" t="str" cm="1">
+        <f t="array" ref="U9">_xlfn.IFS(D9&gt;=50000, "A", D9&gt;=40000, "B", D9&gt;=30000, "C", D9&lt;30000, "D")</f>
+        <v>A</v>
+      </c>
+      <c r="V9" s="7" t="str" cm="1">
+        <f t="array" ref="V9">_xlfn.IFS(G9&gt;=30, "Very Active", G9&gt;=20, "Active", G9&gt;=10, "Moderate", G9&lt;10, "Less Active")</f>
+        <v>Active</v>
+      </c>
+      <c r="W9" s="7" t="str" cm="1">
+        <f t="array" ref="W9">_xlfn.IFS(E9&gt;=5, "Coffee Addict", E9&gt;=4, "Heavy Drinker", E9&gt;=2, "Regular Drinker", E9&lt;2, "light drinker")</f>
+        <v>Regular Drinker</v>
+      </c>
+      <c r="X9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Elgble</v>
+      </c>
+      <c r="Y9" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z9" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Active Employee</v>
+      </c>
+      <c r="AA9" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB9" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Python Performer</v>
+      </c>
+      <c r="AC9" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD9" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Responsible</v>
+      </c>
+      <c r="AE9" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Special Employee</v>
+      </c>
+      <c r="AF9" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Normal</v>
+      </c>
+      <c r="AG9" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH9" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI9" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Technical</v>
+      </c>
+      <c r="AJ9" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>High Performer</v>
+      </c>
+      <c r="AK9" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL9" s="7"/>
+      <c r="AM9" s="7"/>
+      <c r="AN9" s="7"/>
+      <c r="AO9" s="7"/>
+      <c r="AP9" s="7"/>
+      <c r="AQ9" s="7"/>
+      <c r="AR9" s="7"/>
+      <c r="AS9" s="7"/>
+    </row>
+    <row r="10" spans="1:47">
+      <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="1">
         <v>38000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <v>2</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="1">
         <v>18</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="J10" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K10" s="7" t="str">
+        <v>Heavy Coffee Driner</v>
+      </c>
+      <c r="L10" s="7" t="str">
+        <v>Good Attendance</v>
+      </c>
+      <c r="M10" s="7" t="str">
+        <v>Normal  search</v>
+      </c>
+      <c r="N10" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O10" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P10" s="7" t="str">
+        <v xml:space="preserve">Other Mood </v>
+      </c>
+      <c r="Q10" s="7" t="str" cm="1">
+        <f t="array" ref="Q10">_xlfn.IFS(D10&gt;=50000, "Excellent", D10&gt;=40000, "Very Good", D10&gt;=30000, "Good", D10&lt;30000, "Low")</f>
+        <v>Good</v>
+      </c>
+      <c r="R10" s="7" t="str" cm="1">
+        <f t="array" ref="R10">_xlfn.IFS(E10&gt;=5, "Heavy", E10&gt;=3, "Moderate", E10&gt;=1, "Normal", E10=0, "No Coffee")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="S10" s="7" t="str" cm="1">
+        <f t="array" ref="S10">_xlfn.IFS(F11&gt;=5, "Very High", F11&gt;=3, "high", F11&gt;=1, "Moderate", F11=0, "No Bunk")</f>
+        <v>high</v>
+      </c>
+      <c r="T10" s="7" t="str" cm="1">
+        <f t="array" ref="T10">_xlfn.IFS(G10&gt;=30, "Very Hgh", G10&gt;=20, "Hgh", G10&gt;=10, "Moderate", G10&lt;10, "Low")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="U10" s="7" t="str" cm="1">
+        <f t="array" ref="U10">_xlfn.IFS(D10&gt;=50000, "A", D10&gt;=40000, "B", D10&gt;=30000, "C", D10&lt;30000, "D")</f>
+        <v>C</v>
+      </c>
+      <c r="V10" s="7" t="str" cm="1">
+        <f t="array" ref="V10">_xlfn.IFS(G10&gt;=30, "Very Active", G10&gt;=20, "Active", G10&gt;=10, "Moderate", G10&lt;10, "Less Active")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="W10" s="7" t="str" cm="1">
+        <f t="array" ref="W10">_xlfn.IFS(E10&gt;=5, "Coffee Addict", E10&gt;=4, "Heavy Drinker", E10&gt;=2, "Regular Drinker", E10&lt;2, "light drinker")</f>
+        <v>Heavy Drinker</v>
+      </c>
+      <c r="X10" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y10" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z10" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA10" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB10" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC10" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD10" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE10" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF10" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Normal</v>
+      </c>
+      <c r="AG10" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH10" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI10" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Other</v>
+      </c>
+      <c r="AJ10" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK10" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>No Reward</v>
+      </c>
+      <c r="AL10" s="7"/>
+      <c r="AM10" s="7"/>
+      <c r="AN10" s="7"/>
+      <c r="AO10" s="7"/>
+      <c r="AP10" s="7"/>
+      <c r="AQ10" s="7"/>
+      <c r="AR10" s="7"/>
+      <c r="AS10" s="7"/>
+      <c r="AU10" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:47">
+      <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="1">
         <v>42000</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>5</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="1">
         <v>28</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M11" t="s">
+      <c r="J11" s="7" t="str">
+        <v>High Salary</v>
+      </c>
+      <c r="K11" s="7" t="str">
+        <v>Heavy Coffee Driner</v>
+      </c>
+      <c r="L11" s="7" t="str">
+        <v>Poor Attendance</v>
+      </c>
+      <c r="M11" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N11" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O11" s="7" t="str">
+        <v>Pizza lower</v>
+      </c>
+      <c r="P11" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q11" s="7" t="str" cm="1">
+        <f t="array" ref="Q11">_xlfn.IFS(D11&gt;=50000, "Excellent", D11&gt;=40000, "Very Good", D11&gt;=30000, "Good", D11&lt;30000, "Low")</f>
+        <v>Very Good</v>
+      </c>
+      <c r="R11" s="7" t="str" cm="1">
+        <f t="array" ref="R11">_xlfn.IFS(E11&gt;=5, "Heavy", E11&gt;=3, "Moderate", E11&gt;=1, "Normal", E11=0, "No Coffee")</f>
+        <v>Heavy</v>
+      </c>
+      <c r="S11" s="7" t="str" cm="1">
+        <f t="array" ref="S11">_xlfn.IFS(F12&gt;=5, "Very High", F12&gt;=3, "high", F12&gt;=1, "Moderate", F12=0, "No Bunk")</f>
+        <v>high</v>
+      </c>
+      <c r="T11" s="7" t="str" cm="1">
+        <f t="array" ref="T11">_xlfn.IFS(G11&gt;=30, "Very Hgh", G11&gt;=20, "Hgh", G11&gt;=10, "Moderate", G11&lt;10, "Low")</f>
+        <v>Hgh</v>
+      </c>
+      <c r="U11" s="7" t="str" cm="1">
+        <f t="array" ref="U11">_xlfn.IFS(D11&gt;=50000, "A", D11&gt;=40000, "B", D11&gt;=30000, "C", D11&lt;30000, "D")</f>
+        <v>B</v>
+      </c>
+      <c r="V11" s="7" t="str" cm="1">
+        <f t="array" ref="V11">_xlfn.IFS(G11&gt;=30, "Very Active", G11&gt;=20, "Active", G11&gt;=10, "Moderate", G11&lt;10, "Less Active")</f>
+        <v>Active</v>
+      </c>
+      <c r="W11" s="7" t="str" cm="1">
+        <f t="array" ref="W11">_xlfn.IFS(E11&gt;=5, "Coffee Addict", E11&gt;=4, "Heavy Drinker", E11&gt;=2, "Regular Drinker", E11&lt;2, "light drinker")</f>
+        <v>Coffee Addict</v>
+      </c>
+      <c r="X11" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y11" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Attenton</v>
+      </c>
+      <c r="Z11" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA11" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB11" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC11" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Pizza Fan</v>
+      </c>
+      <c r="AD11" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE11" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF11" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Food &amp; Coffee Lover</v>
+      </c>
+      <c r="AG11" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH11" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI11" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Other</v>
+      </c>
+      <c r="AJ11" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK11" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
+      <c r="AN11" s="7"/>
+      <c r="AO11" s="7"/>
+      <c r="AP11" s="7"/>
+      <c r="AQ11" s="7"/>
+      <c r="AR11" s="7"/>
+      <c r="AS11" s="7"/>
+      <c r="AU11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:47">
+      <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="1">
         <v>29000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="1">
         <v>4</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="1">
         <v>22</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="3" t="s">
+      <c r="J12" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K12" s="7" t="str">
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L12" s="7" t="str">
+        <v>Poor Attendance</v>
+      </c>
+      <c r="M12" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N12" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O12" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P12" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q12" s="7" t="str" cm="1">
+        <f t="array" ref="Q12">_xlfn.IFS(D12&gt;=50000, "Excellent", D12&gt;=40000, "Very Good", D12&gt;=30000, "Good", D12&lt;30000, "Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="R12" s="7" t="str" cm="1">
+        <f t="array" ref="R12">_xlfn.IFS(E12&gt;=5, "Heavy", E12&gt;=3, "Moderate", E12&gt;=1, "Normal", E12=0, "No Coffee")</f>
+        <v>Normal</v>
+      </c>
+      <c r="S12" s="7" t="str" cm="1">
+        <f t="array" ref="S12">_xlfn.IFS(F13&gt;=5, "Very High", F13&gt;=3, "high", F13&gt;=1, "Moderate", F13=0, "No Bunk")</f>
+        <v>No Bunk</v>
+      </c>
+      <c r="T12" s="7" t="str" cm="1">
+        <f t="array" ref="T12">_xlfn.IFS(G12&gt;=30, "Very Hgh", G12&gt;=20, "Hgh", G12&gt;=10, "Moderate", G12&lt;10, "Low")</f>
+        <v>Hgh</v>
+      </c>
+      <c r="U12" s="7" t="str" cm="1">
+        <f t="array" ref="U12">_xlfn.IFS(D12&gt;=50000, "A", D12&gt;=40000, "B", D12&gt;=30000, "C", D12&lt;30000, "D")</f>
+        <v>D</v>
+      </c>
+      <c r="V12" s="7" t="str" cm="1">
+        <f t="array" ref="V12">_xlfn.IFS(G12&gt;=30, "Very Active", G12&gt;=20, "Active", G12&gt;=10, "Moderate", G12&lt;10, "Less Active")</f>
+        <v>Active</v>
+      </c>
+      <c r="W12" s="7" t="str" cm="1">
+        <f t="array" ref="W12">_xlfn.IFS(E12&gt;=5, "Coffee Addict", E12&gt;=4, "Heavy Drinker", E12&gt;=2, "Regular Drinker", E12&lt;2, "light drinker")</f>
+        <v>light drinker</v>
+      </c>
+      <c r="X12" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y12" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z12" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA12" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB12" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC12" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD12" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE12" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF12" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Normal</v>
+      </c>
+      <c r="AG12" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH12" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Other Mood</v>
+      </c>
+      <c r="AI12" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Technical</v>
+      </c>
+      <c r="AJ12" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK12" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>No Reward</v>
+      </c>
+      <c r="AL12" s="7"/>
+      <c r="AM12" s="7"/>
+      <c r="AN12" s="7"/>
+      <c r="AO12" s="7"/>
+      <c r="AP12" s="7"/>
+      <c r="AQ12" s="7"/>
+      <c r="AR12" s="7"/>
+      <c r="AS12" s="7"/>
+    </row>
+    <row r="13" spans="1:47">
+      <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
         <v>55000</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>3</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="1">
         <v>0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="1">
         <v>40</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="J13" s="7" t="str">
+        <v>High Salary</v>
+      </c>
+      <c r="K13" s="7" t="str">
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L13" s="7" t="str">
+        <v>Good Attendance</v>
+      </c>
+      <c r="M13" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N13" s="7" t="str">
+        <v>Pyhton Employee</v>
+      </c>
+      <c r="O13" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P13" s="7" t="str">
+        <v xml:space="preserve">Other Mood </v>
+      </c>
+      <c r="Q13" s="7" t="str" cm="1">
+        <f t="array" ref="Q13">_xlfn.IFS(D13&gt;=50000, "Excellent", D13&gt;=40000, "Very Good", D13&gt;=30000, "Good", D13&lt;30000, "Low")</f>
+        <v>Excellent</v>
+      </c>
+      <c r="R13" s="7" t="str" cm="1">
+        <f t="array" ref="R13">_xlfn.IFS(E13&gt;=5, "Heavy", E13&gt;=3, "Moderate", E13&gt;=1, "Normal", E13=0, "No Coffee")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="S13" s="7" t="str" cm="1">
+        <f t="array" ref="S13">_xlfn.IFS(F14&gt;=5, "Very High", F14&gt;=3, "high", F14&gt;=1, "Moderate", F14=0, "No Bunk")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="T13" s="7" t="str" cm="1">
+        <f t="array" ref="T13">_xlfn.IFS(G13&gt;=30, "Very Hgh", G13&gt;=20, "Hgh", G13&gt;=10, "Moderate", G13&lt;10, "Low")</f>
+        <v>Very Hgh</v>
+      </c>
+      <c r="U13" s="7" t="str" cm="1">
+        <f t="array" ref="U13">_xlfn.IFS(D13&gt;=50000, "A", D13&gt;=40000, "B", D13&gt;=30000, "C", D13&lt;30000, "D")</f>
+        <v>A</v>
+      </c>
+      <c r="V13" s="7" t="str" cm="1">
+        <f t="array" ref="V13">_xlfn.IFS(G13&gt;=30, "Very Active", G13&gt;=20, "Active", G13&gt;=10, "Moderate", G13&lt;10, "Less Active")</f>
+        <v>Very Active</v>
+      </c>
+      <c r="W13" s="7" t="str" cm="1">
+        <f t="array" ref="W13">_xlfn.IFS(E13&gt;=5, "Coffee Addict", E13&gt;=4, "Heavy Drinker", E13&gt;=2, "Regular Drinker", E13&lt;2, "light drinker")</f>
+        <v>Regular Drinker</v>
+      </c>
+      <c r="X13" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Elgble</v>
+      </c>
+      <c r="Y13" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z13" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Active Employee</v>
+      </c>
+      <c r="AA13" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB13" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Python Performer</v>
+      </c>
+      <c r="AC13" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD13" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE13" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Special Employee</v>
+      </c>
+      <c r="AF13" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Normal</v>
+      </c>
+      <c r="AG13" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Very Active</v>
+      </c>
+      <c r="AH13" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI13" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Technical</v>
+      </c>
+      <c r="AJ13" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>High Performer</v>
+      </c>
+      <c r="AK13" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL13" s="7"/>
+      <c r="AM13" s="7"/>
+      <c r="AN13" s="7"/>
+      <c r="AO13" s="7"/>
+      <c r="AP13" s="7"/>
+      <c r="AQ13" s="7"/>
+      <c r="AR13" s="7"/>
+      <c r="AS13" s="7"/>
+      <c r="AU13" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:47">
+      <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="1">
         <v>33000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <v>2</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="1">
         <v>7</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M14" t="s">
+      <c r="J14" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K14" s="7" t="str">
+        <v xml:space="preserve">Normal </v>
+      </c>
+      <c r="L14" s="7" t="str">
+        <v>Good Attendance</v>
+      </c>
+      <c r="M14" s="7" t="str">
+        <v>Normal  search</v>
+      </c>
+      <c r="N14" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O14" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P14" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q14" s="7" t="str" cm="1">
+        <f t="array" ref="Q14">_xlfn.IFS(D14&gt;=50000, "Excellent", D14&gt;=40000, "Very Good", D14&gt;=30000, "Good", D14&lt;30000, "Low")</f>
+        <v>Good</v>
+      </c>
+      <c r="R14" s="7" t="str" cm="1">
+        <f t="array" ref="R14">_xlfn.IFS(E14&gt;=5, "Heavy", E14&gt;=3, "Moderate", E14&gt;=1, "Normal", E14=0, "No Coffee")</f>
+        <v>Normal</v>
+      </c>
+      <c r="S14" s="7" t="str" cm="1">
+        <f t="array" ref="S14">_xlfn.IFS(F15&gt;=5, "Very High", F15&gt;=3, "high", F15&gt;=1, "Moderate", F15=0, "No Bunk")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="T14" s="7" t="str" cm="1">
+        <f t="array" ref="T14">_xlfn.IFS(G14&gt;=30, "Very Hgh", G14&gt;=20, "Hgh", G14&gt;=10, "Moderate", G14&lt;10, "Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="U14" s="7" t="str" cm="1">
+        <f t="array" ref="U14">_xlfn.IFS(D14&gt;=50000, "A", D14&gt;=40000, "B", D14&gt;=30000, "C", D14&lt;30000, "D")</f>
+        <v>C</v>
+      </c>
+      <c r="V14" s="7" t="str" cm="1">
+        <f t="array" ref="V14">_xlfn.IFS(G14&gt;=30, "Very Active", G14&gt;=20, "Active", G14&gt;=10, "Moderate", G14&lt;10, "Less Active")</f>
+        <v>Less Active</v>
+      </c>
+      <c r="W14" s="7" t="str" cm="1">
+        <f t="array" ref="W14">_xlfn.IFS(E14&gt;=5, "Coffee Addict", E14&gt;=4, "Heavy Drinker", E14&gt;=2, "Regular Drinker", E14&lt;2, "light drinker")</f>
+        <v>Regular Drinker</v>
+      </c>
+      <c r="X14" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y14" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z14" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA14" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Happy High Earner</v>
+      </c>
+      <c r="AB14" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC14" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD14" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE14" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF14" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Normal</v>
+      </c>
+      <c r="AG14" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH14" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI14" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Other</v>
+      </c>
+      <c r="AJ14" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK14" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL14" s="7"/>
+      <c r="AM14" s="7"/>
+      <c r="AN14" s="7"/>
+      <c r="AO14" s="7"/>
+      <c r="AP14" s="7"/>
+      <c r="AQ14" s="7"/>
+      <c r="AR14" s="7"/>
+      <c r="AS14" s="7"/>
+      <c r="AU14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:47">
+      <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="1">
         <v>47000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="1">
         <v>4</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="1">
         <v>32</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="3" t="s">
+      <c r="J15" s="7" t="str">
+        <v>High Salary</v>
+      </c>
+      <c r="K15" s="7" t="str">
+        <v>Heavy Coffee Driner</v>
+      </c>
+      <c r="L15" s="7" t="str">
+        <v>Good Attendance</v>
+      </c>
+      <c r="M15" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N15" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O15" s="7" t="str">
+        <v>Pizza lower</v>
+      </c>
+      <c r="P15" s="7" t="str">
+        <v xml:space="preserve">Other Mood </v>
+      </c>
+      <c r="Q15" s="7" t="str" cm="1">
+        <f t="array" ref="Q15">_xlfn.IFS(D15&gt;=50000, "Excellent", D15&gt;=40000, "Very Good", D15&gt;=30000, "Good", D15&lt;30000, "Low")</f>
+        <v>Very Good</v>
+      </c>
+      <c r="R15" s="7" t="str" cm="1">
+        <f t="array" ref="R15">_xlfn.IFS(E15&gt;=5, "Heavy", E15&gt;=3, "Moderate", E15&gt;=1, "Normal", E15=0, "No Coffee")</f>
+        <v>Moderate</v>
+      </c>
+      <c r="S15" s="7" t="str" cm="1">
+        <f t="array" ref="S15">_xlfn.IFS(F16&gt;=5, "Very High", F16&gt;=3, "high", F16&gt;=1, "Moderate", F16=0, "No Bunk")</f>
+        <v>Very High</v>
+      </c>
+      <c r="T15" s="7" t="str" cm="1">
+        <f t="array" ref="T15">_xlfn.IFS(G15&gt;=30, "Very Hgh", G15&gt;=20, "Hgh", G15&gt;=10, "Moderate", G15&lt;10, "Low")</f>
+        <v>Very Hgh</v>
+      </c>
+      <c r="U15" s="7" t="str" cm="1">
+        <f t="array" ref="U15">_xlfn.IFS(D15&gt;=50000, "A", D15&gt;=40000, "B", D15&gt;=30000, "C", D15&lt;30000, "D")</f>
+        <v>B</v>
+      </c>
+      <c r="V15" s="7" t="str" cm="1">
+        <f t="array" ref="V15">_xlfn.IFS(G15&gt;=30, "Very Active", G15&gt;=20, "Active", G15&gt;=10, "Moderate", G15&lt;10, "Less Active")</f>
+        <v>Very Active</v>
+      </c>
+      <c r="W15" s="7" t="str" cm="1">
+        <f t="array" ref="W15">_xlfn.IFS(E15&gt;=5, "Coffee Addict", E15&gt;=4, "Heavy Drinker", E15&gt;=2, "Regular Drinker", E15&lt;2, "light drinker")</f>
+        <v>Heavy Drinker</v>
+      </c>
+      <c r="X15" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y15" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+      <c r="Z15" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Active Employee</v>
+      </c>
+      <c r="AA15" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB15" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC15" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD15" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE15" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF15" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Food &amp; Coffee Lover</v>
+      </c>
+      <c r="AG15" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Very Active</v>
+      </c>
+      <c r="AH15" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Good Mood</v>
+      </c>
+      <c r="AI15" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Other</v>
+      </c>
+      <c r="AJ15" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>High Performer</v>
+      </c>
+      <c r="AK15" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Reward</v>
+      </c>
+      <c r="AL15" s="7"/>
+      <c r="AM15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AO15" s="7"/>
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="7"/>
+      <c r="AR15" s="7"/>
+      <c r="AS15" s="7"/>
+    </row>
+    <row r="16" spans="1:47">
+      <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="1">
         <v>27000</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
         <v>5</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="1">
         <v>5</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="1">
         <v>27</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="J16" s="7" t="str">
+        <v>Normal salary</v>
+      </c>
+      <c r="K16" s="7" t="str">
+        <v>Heavy Coffee Driner</v>
+      </c>
+      <c r="L16" s="7" t="str">
+        <v>Poor Attendance</v>
+      </c>
+      <c r="M16" s="7" t="str">
+        <v>High Search</v>
+      </c>
+      <c r="N16" s="7" t="str">
+        <v xml:space="preserve">Other Department </v>
+      </c>
+      <c r="O16" s="7" t="str">
+        <v>Other Food</v>
+      </c>
+      <c r="P16" s="7" t="str">
+        <v>Good Mood</v>
+      </c>
+      <c r="Q16" s="7" t="str" cm="1">
+        <f t="array" ref="Q16">_xlfn.IFS(D16&gt;=50000, "Excellent", D16&gt;=40000, "Very Good", D16&gt;=30000, "Good", D16&lt;30000, "Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="R16" s="7" t="str" cm="1">
+        <f t="array" ref="R16">_xlfn.IFS(E16&gt;=5, "Heavy", E16&gt;=3, "Moderate", E16&gt;=1, "Normal", E16=0, "No Coffee")</f>
+        <v>Heavy</v>
+      </c>
+      <c r="S16" s="7" t="str" cm="1">
+        <f t="array" ref="S16">_xlfn.IFS(F17&gt;=5, "Very High", F17&gt;=3, "high", F17&gt;=1, "Moderate", F17=0, "No Bunk")</f>
+        <v>No Bunk</v>
+      </c>
+      <c r="T16" s="7" t="str" cm="1">
+        <f t="array" ref="T16">_xlfn.IFS(G16&gt;=30, "Very Hgh", G16&gt;=20, "Hgh", G16&gt;=10, "Moderate", G16&lt;10, "Low")</f>
+        <v>Hgh</v>
+      </c>
+      <c r="U16" s="7" t="str" cm="1">
+        <f t="array" ref="U16">_xlfn.IFS(D16&gt;=50000, "A", D16&gt;=40000, "B", D16&gt;=30000, "C", D16&lt;30000, "D")</f>
+        <v>D</v>
+      </c>
+      <c r="V16" s="7" t="str" cm="1">
+        <f t="array" ref="V16">_xlfn.IFS(G16&gt;=30, "Very Active", G16&gt;=20, "Active", G16&gt;=10, "Moderate", G16&lt;10, "Less Active")</f>
+        <v>Active</v>
+      </c>
+      <c r="W16" s="7" t="str" cm="1">
+        <f t="array" ref="W16">_xlfn.IFS(E16&gt;=5, "Coffee Addict", E16&gt;=4, "Heavy Drinker", E16&gt;=2, "Regular Drinker", E16&lt;2, "light drinker")</f>
+        <v>Coffee Addict</v>
+      </c>
+      <c r="X16" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Elgble</v>
+      </c>
+      <c r="Y16" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Attenton</v>
+      </c>
+      <c r="Z16" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>inactive</v>
+      </c>
+      <c r="AA16" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Normal Employee</v>
+      </c>
+      <c r="AB16" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Other</v>
+      </c>
+      <c r="AC16" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>Not Pizza Fan</v>
+      </c>
+      <c r="AD16" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="AE16" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Regular Employee</v>
+      </c>
+      <c r="AF16" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v>Food &amp; Coffee Lover</v>
+      </c>
+      <c r="AG16" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Normal</v>
+      </c>
+      <c r="AH16" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>Other Mood</v>
+      </c>
+      <c r="AI16" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Technical</v>
+      </c>
+      <c r="AJ16" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Regular Performer</v>
+      </c>
+      <c r="AK16" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>No Reward</v>
+      </c>
+      <c r="AL16" s="7"/>
+      <c r="AM16" s="7"/>
+      <c r="AN16" s="7"/>
+      <c r="AO16" s="7"/>
+      <c r="AP16" s="7"/>
+      <c r="AQ16" s="7"/>
+      <c r="AR16" s="7"/>
+      <c r="AS16" s="7"/>
+      <c r="AU16" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="M17" t="s">
+    <row r="17" spans="1:47">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="AU17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="M19" s="4" t="s">
+    <row r="19" spans="1:47">
+      <c r="AU19" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="M20" t="s">
+    <row r="20" spans="1:47">
+      <c r="AU20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:47">
+      <c r="A21" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="6"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:47">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:47">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
@@ -2651,7 +4647,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:47">
       <c r="A24" s="1" t="s">
         <v>66</v>
       </c>
@@ -2659,7 +4655,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:47">
       <c r="A25" s="1" t="s">
         <v>68</v>
       </c>
@@ -2667,7 +4663,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:47">
       <c r="A26" s="1" t="s">
         <v>70</v>
       </c>
@@ -2675,7 +4671,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:47">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -2683,17 +4679,17 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:47">
+      <c r="A30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="6"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:47">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:47">
       <c r="A32" s="2" t="s">
         <v>75</v>
       </c>
@@ -2734,14 +4730,14 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="6"/>
+      <c r="B39" s="5"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2" t="s">
@@ -2784,14 +4780,14 @@
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="6"/>
+      <c r="B49" s="5"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
@@ -2834,14 +4830,14 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="6"/>
+      <c r="B59" s="5"/>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2" t="s">
@@ -2884,14 +4880,14 @@
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="6"/>
+      <c r="B68" s="5"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2" t="s">
@@ -2934,14 +4930,14 @@
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B78" s="6"/>
+      <c r="B78" s="5"/>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2" t="s">
@@ -2984,7 +4980,7 @@
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="3" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2994,7 +4990,7 @@
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="3" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3004,7 +5000,7 @@
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="3" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3014,7 +5010,7 @@
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3024,7 +5020,7 @@
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="3" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3034,7 +5030,7 @@
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="3" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3044,7 +5040,7 @@
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="3" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3054,7 +5050,7 @@
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="3" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3064,7 +5060,7 @@
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="3" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3074,7 +5070,7 @@
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="3" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3084,7 +5080,7 @@
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="3" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3094,7 +5090,7 @@
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="3" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3104,7 +5100,7 @@
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3114,7 +5110,7 @@
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="3" t="s">
         <v>140</v>
       </c>
     </row>
